--- a/results/clinical_variables_data.xlsx
+++ b/results/clinical_variables_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos Paja Suarez\imoc_pdac\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B48333-89EC-4BAE-9FF9-B02300A89B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BD7FE7-2582-44C0-B5B4-3CAF0B7A5DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0AE20B98-A0B6-4877-AEB3-B14B3A382150}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0AE20B98-A0B6-4877-AEB3-B14B3A382150}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
   <si>
     <t>Variable name</t>
   </si>
   <si>
-    <t>Patient ID</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Diagnosis Age</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>Primary Therapy Outcome Success Type</t>
   </si>
   <si>
-    <t>Cluster</t>
-  </si>
-  <si>
     <t>Categorical</t>
   </si>
   <si>
@@ -192,9 +186,6 @@
   </si>
   <si>
     <t>Body of Pancreas; Head of Pancreas; Other (please specify); Tail of Pancreas</t>
-  </si>
-  <si>
-    <t>1; 2</t>
   </si>
   <si>
     <t>Yes, History of Prior Malignancy; No</t>
@@ -282,19 +273,67 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="15" formatCode="0.00E+00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -305,6 +344,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EC48E2A5-9502-46A1-BD59-4959D65DAF3F}" name="Tabla2" displayName="Tabla2" ref="A1:E30" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:E30" xr:uid="{EC48E2A5-9502-46A1-BD59-4959D65DAF3F}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{CB614EA2-01D8-478D-A30C-17822D35AA95}" name="Variable name" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{CF410121-8B9C-4E99-8001-BDFB2D583E40}" name="Type of variable" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{76E12B45-6AE3-4959-92DB-96045ACD3F4A}" name="Possible values" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{936C2A78-C6C1-4064-AA38-9474FFF3639E}" name="Statistical test" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{0207C586-06F3-48AD-A11D-9428C67152F1}" name="P-value (adjusted)" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -624,536 +677,523 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45625E-7F74-46B9-96AE-34A54ED11B7B}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="58.33203125" customWidth="1"/>
+    <col min="1" max="1" width="59" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="44.77734375" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="4">
+        <v>3.1699999999999998E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3.8600000000000001E-14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.67600000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.67600000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.60699999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.60699999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.60699999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.60699999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.60699999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="6">
+      <c r="E20" s="4">
         <v>3.1699999999999998E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="6">
-        <v>3.8600000000000001E-14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="5">
         <v>0.67600000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="5">
+        <v>5.9400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.67600000000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.46899999999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="3">
+      <c r="D28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.71499999999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="5">
         <v>0.67600000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.60699999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.60699999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0.60699999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0.60699999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0.60699999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="6">
-        <v>3.1699999999999998E-5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0.67600000000000005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="3">
-        <v>5.9400000000000001E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" t="s">
+    <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0.67600000000000005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" t="s">
-        <v>61</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0.46899999999999997</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="3">
+      <c r="D30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="5">
         <v>0.71499999999999997</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0.67600000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0.71499999999999997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>